--- a/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
+++ b/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,8 +559,6 @@
           <t>Amherst</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>amherstminorbasketball@gmail.com</t>
@@ -631,8 +631,6 @@
           <t>Amherst (Cumberland NS – Westmorland NB border region; trains around Sackville NB)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>jrmountiesbasketball@gmail.com</t>
@@ -705,8 +703,6 @@
           <t>Annapolis County</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>steveyoung902@gmail.com</t>
@@ -784,7 +780,6 @@
           <t>P.O. Box 1241, Antigonish, NS B2G 2L6</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>antigonishbasketball@gmail.com</t>
@@ -857,8 +852,6 @@
           <t>Bedford</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>bmbaregistrar@gmail.com</t>
@@ -931,8 +924,6 @@
           <t>Bedford</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>bmbaregistration@gmail.com</t>
@@ -1005,8 +996,6 @@
           <t>Berwick / Coldbrook (western Kings County)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>tanya.berry@gbstech.com</t>
@@ -1052,7 +1041,6 @@
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1177,7 +1165,6 @@
           <t>https://southshorelightning.ca/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Club/rep teams U12, U15, U16/17; Junior Lightning camps; 3-week summer program; Jr NBA program; private training offering</t>
@@ -1235,13 +1222,11 @@
           <t>Coldbrook/Berwick area (serves Coldbrook, Cambridge, Somerset, Berwick)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>902-678-8466</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>https://kmbagators.wixsite.com/kmba</t>
@@ -1257,7 +1242,6 @@
           <t>Community basketball ages 5+; long-term athletic development focus; games at New Minas, Port Williams, Windsor Elementary</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -1278,7 +1262,6 @@
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1383,8 +1366,6 @@
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>ortizalanm38@gmail.com</t>
@@ -1430,7 +1411,6 @@
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1453,20 +1433,16 @@
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>shelleyleblanc19@outlook.com</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Shelley Leblanc — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
@@ -1477,7 +1453,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -1515,8 +1490,6 @@
           <t>Dartmouth</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>dartmouthceltics@gmail.com</t>
@@ -1589,7 +1562,6 @@
           <t>Dartmouth</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>902-817-3594</t>
@@ -1667,8 +1639,6 @@
           <t>East Hants</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>president@ehhavoc.org</t>
@@ -1714,7 +1684,6 @@
           <t>https://www.ehhavoc.org/havoc/</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1737,8 +1706,6 @@
           <t>East Hants (Enfield/Elmsdale)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
@@ -1811,14 +1778,11 @@
           <t>East Preston</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>prestonreccentre@gmail.com</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Charnell Colley — club contact per Basketball Nova Scotia registry (Preston Recreation Centre); role title not published</t>
@@ -1839,7 +1803,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1877,8 +1840,6 @@
           <t>Enfield / Municipality of East Hants</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
@@ -1889,7 +1850,6 @@
           <t>https://tricountytigers.ca/</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Nonprofit (formerly Tri-County Basketball Association); competitive U10-U18 boys &amp; girls teams; Jr NBA ages 5-10; sessions, camps and events; formal constitution/bylaws</t>
@@ -1952,7 +1912,6 @@
           <t>PO Box 2072, Fall River, NS B2T 1K6</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>president@fallriverrebels.com</t>
@@ -2137,13 +2096,11 @@
           <t>Youth-centre charity serving Glace Bay, New Waterford and surrounding CBRM; recreational basketball among activities (also floor hockey, crossfit)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2181,7 +2138,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>(782) 234-7481</t>
@@ -2341,8 +2297,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>info@fiftyforfree.com</t>
@@ -2363,7 +2317,6 @@
           <t>Free 4-week summer camp (Mon-Fri) for ages 13-19 combining high-level basketball training with financial-literacy and professional-development curriculum</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>community nonprofit (free program, not a league club)</t>
@@ -2411,8 +2364,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>hhbasketballclub@gmail.com</t>
@@ -2525,7 +2476,6 @@
           <t>private academy</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2563,8 +2513,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>HWCBBC@gmail.com</t>
@@ -2585,13 +2533,11 @@
           <t>Wheelchair basketball (parasport); age range not published — may be mixed youth/adult</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>community nonprofit (parasport)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -2634,7 +2580,6 @@
           <t>5604 Morris Street, Halifax, NS B3J 1C2</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>dgt@c-ntr-l.org</t>
@@ -2645,13 +2590,11 @@
           <t>https://highlevelbasketball.org/</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Private training academy: small-group sessions (max 6, grade 5+), 1-on-1/semi-private training, 4-week structured programs, summer camp 2026. No league teams found</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -2699,13 +2642,11 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>902-471-4023</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>https://www.thunderselects.ca/</t>
@@ -2746,7 +2687,6 @@
           <t>https://www.thunderselects.ca/</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2851,14 +2791,11 @@
           <t>Halifax (HRM — exact community unverified)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>sandiehebb@gmail.com</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Sandie Hebb — club contact (BNS registry)</t>
@@ -2879,7 +2816,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2917,8 +2853,6 @@
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
@@ -2991,8 +2925,6 @@
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
@@ -3065,8 +2997,6 @@
           <t>Halifax (west end)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>president@westendsteelers.com</t>
@@ -3139,8 +3069,6 @@
           <t>Halifax/Dartmouth (Greater HRM)</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>cgabriel901@gmail.com</t>
@@ -3213,14 +3141,11 @@
           <t>Hantsport</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>902-684-9672</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Renda Vandertoorn — contact (Valley Family Fun directory)</t>
@@ -3231,13 +3156,11 @@
           <t>Youth leagues in Hantsport</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3275,8 +3198,6 @@
           <t>Inverness</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>philblackwood@gmail.com</t>
@@ -3349,8 +3270,6 @@
           <t>Kentville</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>shotclock2016@gmail.com</t>
@@ -3361,7 +3280,6 @@
           <t>https://www.facebook.com/BasetballAssociationofKentville/</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>House leagues for children aged 5+ in Kentville (the 'Basketball Association of Kentville' house league already mapped as a league)</t>
@@ -3424,14 +3342,11 @@
           <t>Kentville, NS B4N 1T6</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>https://www.sportsengine.com/org/kentville-wildcats-basketball</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Rep/travel youth teams under 'Kentville Minor Basketball Association'; historical entries in BNS provincials (GOALLINE era); legacy 'Jr Axewomen &amp; Kentville Wildcats' eteamz site</t>
@@ -3489,8 +3404,6 @@
           <t>Kentville (serves Hantsport to New Minas corridor)</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
@@ -3501,7 +3414,6 @@
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>U8, U10 (3x3), U12, U14, U16 + STRIVE competitive stream; ~$5/athlete/hr pricing; financial assistance program; formed from merger of Hantsport Minor Basketball, Port Williams Hawks, and Acadia Minor Basketball; partnership with Acadia University</t>
@@ -3559,8 +3471,6 @@
           <t>Kingston / Greenwood</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>jodie-richardson@hotmail.com</t>
@@ -3633,8 +3543,6 @@
           <t>Liverpool (Region of Queens)</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>gerryfaber@hotmail.com</t>
@@ -3707,8 +3615,6 @@
           <t>Lower Sackville</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>president@sackvillestorm.com</t>
@@ -3754,7 +3660,6 @@
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3777,8 +3682,6 @@
           <t>Margaree</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>margareemountainlionsbball@gmail.com</t>
@@ -3866,20 +3769,16 @@
           <t>northshorereccentre@gmail.com</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Richard Halverson, Manager</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3917,8 +3816,6 @@
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>hislopjw@gmail.com</t>
@@ -3964,7 +3861,6 @@
           <t>https://www.pictoucountylightning.com/</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3987,8 +3883,6 @@
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>sports3taxi@hotmail.com</t>
@@ -4019,7 +3913,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4057,8 +3950,6 @@
           <t>North Preston</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>northprestonbulls@gmail.com</t>
@@ -4089,7 +3980,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4127,8 +4017,6 @@
           <t>North Sydney / Northside area, Cape Breton</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>aronashton4@gmail.com</t>
@@ -4159,7 +4047,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4197,14 +4084,11 @@
           <t>Oxford</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>oxfordminorhoops@gmail.com</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Michelle Embree — club contact (BNS member registry)</t>
@@ -4225,7 +4109,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4263,8 +4146,6 @@
           <t>Prospect Road area (Halifax)</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>prospectbulls1@gmail.com</t>
@@ -4310,7 +4191,6 @@
           <t>https://www.prospectbulls.ca/</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4333,8 +4213,6 @@
           <t>Shelburne / Shelburne County</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>beth.shelburnebasketball@gmail.com</t>
@@ -4407,25 +4285,21 @@
           <t>Shubenacadie / East Hants</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>902-750-0619</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>http://www.ehhavoc.org/</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Volunteer-run society; Havoc Recreational League (equal-playing-time house league; registration delayed to 2025 for volunteer shortage); has fielded competitive teams (e.g. Havoc U16)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>community nonprofit</t>
@@ -4473,8 +4347,6 @@
           <t>Sydney</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>cbdreambasketball@gmail.com</t>
@@ -4552,7 +4424,6 @@
           <t>Former Bridgeport school, Glace Bay, NS (training hub); summer programs held at Cape Breton University, Sydney</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Summer2026@basketballcapebreton.com</t>
@@ -4630,7 +4501,6 @@
           <t>St. Margaret's Centre (12 Westwood Blvd area, Upper Tantallon) — street address not published on site</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>information@slambasketball.ca</t>
@@ -4718,7 +4588,6 @@
           <t>northshoresonicsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Dan MacDonald — club contact (BNS member registry)</t>
@@ -4739,7 +4608,6 @@
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4777,8 +4645,6 @@
           <t>Truro</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>cba.trurobball@gmail.com</t>
@@ -4963,13 +4829,11 @@
           <t>Training camps and clinics for young players, beginner to advanced; no evidence of fielding league teams</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5012,7 +4876,6 @@
           <t>West Hants Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>shootingstar@shootingstarbasketball.ca</t>
@@ -5095,7 +4958,6 @@
           <t>1-902-670-7936</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>https://www.acadiaminorbasketball.ca/</t>
@@ -5111,13 +4973,11 @@
           <t>Community club for Wolfville and area, 'programs for kids grade 1+' — opportunities to learn, play and develop regardless of age, gender or ability</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5155,8 +5015,6 @@
           <t>Wolfville</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
@@ -5202,7 +5060,6 @@
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5225,8 +5082,6 @@
           <t>Yarmouth</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>yarmouthminorbasketball@gmail.com</t>
@@ -5524,7 +5379,6 @@
           <t>Halifax (Canada Games Centre field house)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Summer — July 4-6, 2025; 2026 edition scheduled with schedule published on BNS RAMP site</t>
@@ -5644,7 +5498,6 @@
           <t>Cape Breton (Sydney area)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Summer (July–August); 2026 camps July 6-17, tip-off sessions July 2-3</t>
@@ -5702,7 +5555,6 @@
           <t>Cape Breton (New Waterford Community Centre Hub, PUSH Arena, C200; Glace Bay tournament)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Four training seasons (winter/spring/summer/fall; summer 2026 starts July 19); Canada Day Classic tournament July 4-6, 2025 (U12–U18 boys &amp; girls)</t>
@@ -5760,7 +5612,6 @@
           <t>Halifax (Ummah Community Centre, 2510 Matthias St, Halifax B3L 0A9)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>8 Saturdays, May 8 – June 26 (page dated 2021); $250+HST per player incl. adidas uniform</t>
@@ -5828,8 +5679,6 @@
           <t>School-year prep season (fall–spring) with national travel</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5872,9 +5721,6 @@
           <t>Kentville, Annapolis Valley</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>shotclock2016@gmail.com</t>
@@ -5922,14 +5768,11 @@
           <t>Windsor / West Hants, Annapolis Valley</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>RAMP InterActive (shootingstarbasketball.ca is 'Website by RAMP InterActive')</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5962,16 +5805,11 @@
           <t>local (Halifax community league)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -8223,7 +8061,6 @@
           <t>Amherst</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>amherstminorbasketball@gmail.com</t>
@@ -8251,7 +8088,6 @@
           <t>Amherst (Cumberland NS – Westmorland NB border region; trains around Sackville NB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>jrmountiesbasketball@gmail.com</t>
@@ -8279,7 +8115,6 @@
           <t>Annapolis County</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>steveyoung902@gmail.com</t>
@@ -8307,7 +8142,6 @@
           <t>Antigonish</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>antigonishbasketball@gmail.com</t>
@@ -8335,7 +8169,6 @@
           <t>Bedford</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>bmbaregistrar@gmail.com</t>
@@ -8363,7 +8196,6 @@
           <t>Bedford</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>bmbaregistration@gmail.com</t>
@@ -8391,7 +8223,6 @@
           <t>Berwick / Coldbrook (western Kings County)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>tanya.berry@gbstech.com</t>
@@ -8461,7 +8292,6 @@
           <t>southshorelightning@gmail.com</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>https://southshorelightning.ca/</t>
@@ -8484,7 +8314,6 @@
           <t>902-678-8466</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Kevin Hayes — registration contact (role not published)</t>
@@ -8539,7 +8368,6 @@
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>ortizalanm38@gmail.com</t>
@@ -8567,7 +8395,6 @@
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>shelleyleblanc19@outlook.com</t>
@@ -8578,7 +8405,6 @@
           <t>Shelley Leblanc — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8591,7 +8417,6 @@
           <t>Dartmouth</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>dartmouthceltics@gmail.com</t>
@@ -8651,7 +8476,6 @@
           <t>East Hants</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>president@ehhavoc.org</t>
@@ -8679,7 +8503,6 @@
           <t>East Hants (Enfield/Elmsdale)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
@@ -8707,7 +8530,6 @@
           <t>East Preston</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>prestonreccentre@gmail.com</t>
@@ -8718,7 +8540,6 @@
           <t>Charnell Colley — club contact per Basketball Nova Scotia registry (Preston Recreation Centre); role title not published</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8731,13 +8552,11 @@
           <t>Enfield / Municipality of East Hants</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>https://tricountytigers.ca/</t>
@@ -8755,7 +8574,6 @@
           <t>Fall River</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>president@fallriverrebels.com</t>
@@ -8911,7 +8729,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>info@fiftyforfree.com</t>
@@ -8939,7 +8756,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>hhbasketballclub@gmail.com</t>
@@ -8999,7 +8815,6 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>HWCBBC@gmail.com</t>
@@ -9027,13 +8842,11 @@
           <t>Halifax</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>dgt@c-ntr-l.org</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>https://highlevelbasketball.org/</t>
@@ -9056,7 +8869,6 @@
           <t>902-471-4023</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Brandon Rafuse — Founder &amp; Director</t>
@@ -9111,7 +8923,6 @@
           <t>Halifax (HRM — exact community unverified)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>sandiehebb@gmail.com</t>
@@ -9122,7 +8933,6 @@
           <t>Sandie Hebb — club contact (BNS registry)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9135,7 +8945,6 @@
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
@@ -9163,7 +8972,6 @@
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
@@ -9191,7 +8999,6 @@
           <t>Halifax (west end)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>president@westendsteelers.com</t>
@@ -9219,7 +9026,6 @@
           <t>Halifax/Dartmouth (Greater HRM)</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>cgabriel901@gmail.com</t>
@@ -9252,13 +9058,11 @@
           <t>902-684-9672</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Renda Vandertoorn — contact (Valley Family Fun directory)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9271,7 +9075,6 @@
           <t>Inverness</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>philblackwood@gmail.com</t>
@@ -9299,13 +9102,11 @@
           <t>Kentville</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>shotclock2016@gmail.com</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>https://www.facebook.com/BasetballAssociationofKentville/</t>
@@ -9323,13 +9124,11 @@
           <t>Kentville (serves Hantsport to New Minas corridor)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>https://www.axebasketball.ca/</t>
@@ -9347,7 +9146,6 @@
           <t>Kingston / Greenwood</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>jodie-richardson@hotmail.com</t>
@@ -9375,7 +9173,6 @@
           <t>Liverpool (Region of Queens)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>gerryfaber@hotmail.com</t>
@@ -9403,7 +9200,6 @@
           <t>Lower Sackville</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>president@sackvillestorm.com</t>
@@ -9431,7 +9227,6 @@
           <t>Margaree</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>margareemountainlionsbball@gmail.com</t>
@@ -9474,7 +9269,6 @@
           <t>Richard Halverson, Manager</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9487,7 +9281,6 @@
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>hislopjw@gmail.com</t>
@@ -9515,7 +9308,6 @@
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>sports3taxi@hotmail.com</t>
@@ -9543,7 +9335,6 @@
           <t>North Preston</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>northprestonbulls@gmail.com</t>
@@ -9571,7 +9362,6 @@
           <t>North Sydney / Northside area, Cape Breton</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>aronashton4@gmail.com</t>
@@ -9599,7 +9389,6 @@
           <t>Oxford</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>oxfordminorhoops@gmail.com</t>
@@ -9610,7 +9399,6 @@
           <t>Michelle Embree — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9623,7 +9411,6 @@
           <t>Prospect Road area (Halifax)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>prospectbulls1@gmail.com</t>
@@ -9651,7 +9438,6 @@
           <t>Shelburne / Shelburne County</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>beth.shelburnebasketball@gmail.com</t>
@@ -9684,8 +9470,6 @@
           <t>902-750-0619</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>http://www.ehhavoc.org/</t>
@@ -9703,7 +9487,6 @@
           <t>Sydney</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>cbdreambasketball@gmail.com</t>
@@ -9731,7 +9514,6 @@
           <t>Sydney / Glace Bay (CBRM)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Summer2026@basketballcapebreton.com</t>
@@ -9759,7 +9541,6 @@
           <t>Tantallon / St. Margaret's Bay</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>information@slambasketball.ca</t>
@@ -9802,7 +9583,6 @@
           <t>Dan MacDonald — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9815,7 +9595,6 @@
           <t>Truro</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>cba.trurobball@gmail.com</t>
@@ -9907,7 +9686,6 @@
           <t>Windsor (West Hants)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>shootingstar@shootingstarbasketball.ca</t>
@@ -9940,7 +9718,6 @@
           <t>1-902-670-7936</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Jeff Hanshaw — club contact (role not stated)</t>
@@ -9963,7 +9740,6 @@
           <t>Wolfville</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
@@ -9991,7 +9767,6 @@
           <t>Yarmouth</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>yarmouthminorbasketball@gmail.com</t>
@@ -10012,4 +9787,506 @@
   <autoFilter ref="A1:F65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cole Harbour Rockets</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=58</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bedford Eagles</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>St. Margarets Bay SLAM</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>38</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Halifax Hurricanes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=35</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>West End Steelers</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=33</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sackville Storm</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fall River Rebels</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dartmouth Lakers</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Express Basketball</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Community YMCA Panthers</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dartmouth Celtics</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>East Hants Tigers</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Prospect Bulls</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shooting Star Basketball Association</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Shooting Star Basketball Association h=13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>North Preston Bulls</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shooting Stars</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>South Shore Surf</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AXE Basketball</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>East Preston Pacers</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tri City Vipers</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Norwood Knights</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KMBA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Metro Basketball Association (MBA / Me=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sports Additive Selects</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>South Shore Lightning</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Basketball Cape Breton</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Edge School (Edge Prep)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>National Preparatory Association (NPA)=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Darkside Elite</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Piranha</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PUSH</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Highland Family Hoops</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>King's County Basketball</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlantic Elite Basketball League (AEBL=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C32"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
+++ b/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$65</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:Q66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -902,6 +909,9 @@
           <t>One of the largest HRM clubs; hosts its own Bedford Classic tournament</t>
         </is>
       </c>
+      <c r="Q6" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1123,6 +1133,9 @@
           <t>Successor/rebrand of South Shore Minor Basketball Association (legacy GOALLINE site). Phone/address from legacy listing — reconfirm. | Also listed as: South Shore Surf Minor Basketball</t>
         </is>
       </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1200,6 +1213,9 @@
           <t>Second South Shore club alongside Surf; AEBL-anchored with a training-business flavor (private training). Not on current BNS registry page — verify membership. | Type: rep/club program; registered non-profit founded October 2021 (source: https://southshorelightning.ca/about-club/). Full contact incl. fax 902-677-2731 from https://southshorelightning.ca/contacts/. No president/ED named anywhere on site; staff directory (https://southshorelightning.ca/directory/south-shore-lightning-staff/) lists Bre Haley (Coach/Consultant), Elijah Bond (Coach U14 Boys), Ryan Grezaud (Coach U12 Boys). Competitive intel: registration is self-hosted WPForms on their WordPress site (credit card / e-Transfer / cash) — NO incumbent platform (not RAMP/TeamLinkt/TeamSnap), source: https://southshorelightning.ca/registration/. Programs U8–U18 incl. paid private training and summer camps; games span Bridgewater/Hebbville/HRM/Valley.</t>
         </is>
       </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1540,6 +1556,9 @@
           <t>Site was down (DNS ENOTFOUND) 2026-07-14; Facebook page active. GOALLINE stack = competitive intel</t>
         </is>
       </c>
+      <c r="Q15" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1617,6 +1636,9 @@
           <t>Also has a SportsEngine org directory listing</t>
         </is>
       </c>
+      <c r="Q16" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1756,6 +1778,9 @@
           <t>East Hants sits between Truro and Halifax — check for overlap with the Halifax-region census</t>
         </is>
       </c>
+      <c r="Q18" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1818,6 +1843,9 @@
           <t>Community-rec-centre-based club in a historic African Nova Scotian community; Easter Classic info hosted at liveinfinitus.com/easterclassic</t>
         </is>
       </c>
+      <c r="Q19" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1885,6 +1913,9 @@
           <t>enriched 2026-07-18</t>
         </is>
       </c>
+      <c r="Q20" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1962,6 +1993,9 @@
           <t>Registrar email registrar@fallriverrebels.com also published | Also listed as: Fall River Rebels Basketball Association</t>
         </is>
       </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2275,6 +2309,9 @@
           <t>Registration also done in person at Community YMCA lobby</t>
         </is>
       </c>
+      <c r="Q25" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2414,6 +2451,9 @@
           <t>One of the largest Halifax-peninsula clubs | Also listed as: Halifax Hurricanes Minor Basketball</t>
         </is>
       </c>
+      <c r="Q27" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2831,6 +2871,9 @@
           <t>No club website found; home community within HRM not published — needs follow-up</t>
         </is>
       </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2903,6 +2946,9 @@
           <t>Despite 'Academy' name in BNS registry, self-describes as low-cost community club</t>
         </is>
       </c>
+      <c r="Q34" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2975,6 +3021,9 @@
           <t>Listed as 'Express Basketball Academy' in BNS registry but self-describes as a community club, est. 1999 — not a private academy</t>
         </is>
       </c>
+      <c r="Q35" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3047,6 +3096,9 @@
           <t>GOALLINE stack = competitive intel (one of two GOALLINE clubs in HRM alongside Dartmouth Celtics; BNS Provincials also run on GOALLINE)</t>
         </is>
       </c>
+      <c r="Q36" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3119,6 +3171,9 @@
           <t>Nonprofit status not formally confirmed; operates as a competitive club rather than neighbourhood house-league association</t>
         </is>
       </c>
+      <c r="Q37" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3449,6 +3504,9 @@
           <t>The consolidated Valley club — absorbed three predecessor orgs. Safeguarding policies published (Rule of Two, anti-discrimination).</t>
         </is>
       </c>
+      <c r="Q42" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4474,6 +4532,9 @@
           <t>Largest youth basketball org on Cape Breton Island. CBC (2015) covered its move into former Bridgeport school in Glace Bay. Google-Forms-only registration = greenfield software prospect.</t>
         </is>
       </c>
+      <c r="Q57" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4551,6 +4612,9 @@
           <t>Covers the western HRM commuter belt (Timberlea/Hammonds Plains have no separate club)</t>
         </is>
       </c>
+      <c r="Q58" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4926,6 +4990,9 @@
           <t>Also listed as: Shooting Star Basketball Association</t>
         </is>
       </c>
+      <c r="Q63" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5060,6 +5127,9 @@
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
+      <c r="Q65" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5134,7 +5204,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P66"/>
+  <autoFilter ref="A1:Q66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
+++ b/docs/research/provinces/SportsHub-Nova-Scotia.xlsx
@@ -441,7 +441,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,77 +471,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -556,62 +556,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Amherst</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>amherstminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/amherstminorbasketball</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Andrew Adshade — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Founded 2017, 200+ youth annually; seven divisions U6-U18; house league teams, competitive/rep teams, skills camps; recruiting a Technical Director</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships; Atlantic Elite Basketball League (AEBL)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Google Sites website + Google Forms signup</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/amherstminorbasketball</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Also listed as: Amherst Minor Basketball Association</t>
         </is>
@@ -628,62 +628,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Fundy (Cumberland County)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Amherst (Cumberland NS – Westmorland NB border region; trains around Sackville NB)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>jrmountiesbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://www.jrmountiesbasketball.ca/</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Tom Skabar and Brad Blenkhorn — co-founders (est. 2019 from merger of two local programs)</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Girls-only development program + competitive travel teams; historically U14/U16/U18, current site shows U15 and U18; post-school-season (spring) play</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Website platform unidentified; registration not published</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://www.jrmountiesbasketball.ca/about-us</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Nonprofit society, BNS Fundy-region member; alumnae to Mount Allison WBB and UNB. Straddles NS/NB border — dual-PSO dynamics.</t>
         </is>
@@ -700,62 +700,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Annapolis Valley (Annapolis County)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Annapolis County</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>steveyoung902@gmail.com</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/383677184448811/</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Steve Young — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Listed as a BNS basketball member club; separate FB presence describes a track &amp; field club — appears to be a multi-sport community org with a basketball arm</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Facebook only</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Verify scope by outreach — BNS lists it under Valley region basketball members. | Type: community club (BNS member, Valley region, Fall/Winter). BNS-listed club contact: Steve Young (role not stated) — source: https://basketballnovascotia.ca/content/member-clubs. Only web presence is Facebook group: https://www.facebook.com/groups/383677184448811/. No registration platform identified.</t>
         </is>
@@ -772,67 +772,67 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Antigonish</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>P.O. Box 1241, Antigonish, NS B2G 2L6</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>antigonishbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://playfinder.ca/Org/AntBkblAMBB</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Geoff Spencer — president (2025-26 executive board)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>40+ years serving ages 5-13: Saturday Skills program ($140 base registration), free Girls Basketball Basics for beginners, recreational play, and competitive team play via the Junior X program (five programs total)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships; Atlantic Elite Basketball League (AEBL)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>PlayFinder / My Sport Hub (mysporthub.ca) for schedules; Facebook for comms</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2025-26 board: President Geoff Spencer, Treasurer/Registrar Patrick Withey, Secretary Greg Hadley, Programming Coordinator Bill Hannah, Gear Coordinator Eric Connolly | Also listed as: Antigonish Minor Basketball Association</t>
         </is>
@@ -849,68 +849,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>47</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Bedford</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>bmbaregistrar@gmail.com</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>https://bedfordeagles.ca/</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Brian Allt — club contact/registrar (per BNS registry; also coaches an Eagles MBA team)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>House league (U10-U18 boys &amp; girls), Bedford Elite rep program, Bedford Classic tournament (host), U10 Elite Camp</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + registration + team app)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://bedfordeagles.ca/</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>One of the largest HRM clubs; hosts its own Bedford Classic tournament</t>
         </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -924,62 +924,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Bedford</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>bmbaregistration@gmail.com</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://www.bedfordeagles.ca/</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Brian Allt — club contact per Basketball Nova Scotia registry (also coaches an MBA Eagles team); role title not published</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>House league U10-U18 boys &amp; girls; 'Bedford Elite' rep/competitive program with tryouts across age groups; U10 Bedford Elite camp</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registration, official assigning, team app); registrar email bmbaregistrar@gmail.com on site</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>BNS member club, Central Region</t>
         </is>
@@ -996,57 +996,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Berwick / Coldbrook (western Kings County)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>tanya.berry@gbstech.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Tanya Berry — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Serves Coldbrook, Cambridge, Somerset, Berwick 'and all points in between'; Quickstart ages 5-7, U10 (8-9) and up; season October through BNS provincial tournaments (Mar-Apr); home gyms in Berwick, Coldbrook, Somerset</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wix website; registration platform not identified</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
@@ -1063,78 +1063,78 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Bridgewater</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>86 Winburn Avenue, Bridgewater, NS (from legacy GOALLINE site — verify)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>902-530-2933</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>ssminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://www.southshoresurf.ca/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Corey Lohnes — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Junior High Spring League gr 7-9 (male/female) at Park View Education Centre (Bridgewater); Elementary Spring League gr 2-6 at Bayview Community School (Mahone Bay); winter rep teams</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Google Sites website + RAMP Registration; legacy GOALLINE site (southshoreminorbasketballassociation.goalline.ca, dead)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://www.southshoresurf.ca/</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Successor/rebrand of South Shore Minor Basketball Association (legacy GOALLINE site). Phone/address from legacy listing — reconfirm. | Also listed as: South Shore Surf Minor Basketball</t>
         </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1148,73 +1148,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>South Shore</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Bridgewater / Hebbville area (Lunenburg County)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>15736B Highway 3, Hebbville, NS B4V 6Z7</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>902-350-0027</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>southshorelightning@gmail.com</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://southshorelightning.ca/</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Club/rep teams U12, U15, U16/17; Junior Lightning camps; 3-week summer program; Jr NBA program; private training offering</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Atlantic Elite Basketball League (AEBL)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>WordPress site with built-in registration; platform vendor not identified</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://southshorelightning.ca/</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Second South Shore club alongside Surf; AEBL-anchored with a training-business flavor (private training). Not on current BNS registry page — verify membership. | Type: rep/club program; registered non-profit founded October 2021 (source: https://southshorelightning.ca/about-club/). Full contact incl. fax 902-677-2731 from https://southshorelightning.ca/contacts/. No president/ED named anywhere on site; staff directory (https://southshorelightning.ca/directory/south-shore-lightning-staff/) lists Bre Haley (Coach/Consultant), Elijah Bond (Coach U14 Boys), Ryan Grezaud (Coach U12 Boys). Competitive intel: registration is self-hosted WPForms on their WordPress site (credit card / e-Transfer / cash) — NO incumbent platform (not RAMP/TeamLinkt/TeamSnap), source: https://southshorelightning.ca/registration/. Programs U8–U18 incl. paid private training and summer camps; games span Bridgewater/Hebbville/HRM/Valley.</t>
         </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1228,52 +1228,52 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Annapolis Valley</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Coldbrook/Berwick area (serves Coldbrook, Cambridge, Somerset, Berwick)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>902-678-8466</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Kevin Hayes — registration contact (role not published)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Community basketball ages 5+; long-term athletic development focus; games at New Minas, Port Williams, Windsor Elementary</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wix website; BNS registration via RAMP</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://kmbagators.wixsite.com/kmba</t>
         </is>
@@ -1290,72 +1290,72 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cole Harbour</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>184 Colby Drive, Cole Harbour, NS B2V 1J7</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>902-880-7628</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>president@rocketsbasketball.ca</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>https://www.rocketsbasketball.ca/</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Robin Veinotte — President (BNS registry contact using president@ address)</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Littles/Jr NBA intro; winter house league U10-U18 by age/gender; summer elite travel teams; 'Sprummer' spring/summer league; spring 3x3; shooting clinics</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA); FIBA-format 3x3 (spring, club-run)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registration, communications)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>One of the few HRM clubs publishing full street address and phone</t>
         </is>
@@ -1372,57 +1372,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Fundy (Cumberland County)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>ortizalanm38@gmail.com</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://www.facebook.com/CumberlandCrushers/</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Mike Ortiz — club contact (BNS member registry); Sam Alick — U12 head coach</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Rep/travel teams incl. U12 (2024-25 BNS provincial champions) and U16/U18</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships (U12 / U14 / U16-U18 Provincials); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Facebook only</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
@@ -1439,47 +1439,47 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Fundy (Cumberland County)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Cumberland County (exact town not published)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>shelleyleblanc19@outlook.com</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Shelley Leblanc — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>On BNS member registry (Fundy region) with no link; no independent web presence found. Possibly related to/distinct from Cumberland Crushers — verify by phone.</t>
         </is>
@@ -1496,68 +1496,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Dartmouth</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>dartmouthceltics@gmail.com</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>http://dartmouthceltics.ca/</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>John Morash — club contact per Basketball Nova Scotia registry; role title not published</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Youth teams across MBA age divisions (U10-U18 era teams listed under coach names)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>GOALLINE (dartmouthceltics.ca page.php URLs = 'powered by GOALLINE.ca'); site unreachable (DNS) at research time</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Site was down (DNS ENOTFOUND) 2026-07-14; Facebook page active. GOALLINE stack = competitive intel</t>
         </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1571,73 +1571,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Dartmouth</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>902-817-3594</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>dartmouthlakersbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>https://dartmouthlakers.ca/</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Eric Landovich — club contact per Basketball Nova Scotia registry; role title not published</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Junior Lakers (grades P-2, two 8-week sessions/yr, non-competitive); divisional play ages 8-17 (U10-U18) by gender; est. 2004 from merger of two clubs</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>RAMP InterActive (main website) + TeamLinkt (leagues.teamlinkt.com/dartmouth — league management &amp; registration) + ItemOrder (merch). Dual-platform club — TeamLinkt presence is notable competitive intel</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Also has a SportsEngine org directory listing</t>
         </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -1651,57 +1651,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>East Hants</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>president@ehhavoc.org</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>https://www.ehhavoc.org/havoc/</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Paul Preiss — president (BNS member registry contact)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Youth basketball association in East Hants (second club alongside East Hants Tigers)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>TeamLinkt (site states they switched from TeamSnap to TeamLinkt for registration/association management) — key competitive intel</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://www.ehhavoc.org/havoc/</t>
         </is>
@@ -1718,68 +1718,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>East Hants (Enfield/Elmsdale)</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://tricountytigers.ca/</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Nicki Murphy — registrar (BNS member registry contact)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Competitive U10-U18 boys &amp; girls teams; Jr. NBA developmental program ages 5-10</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + RAMP Registration + RAMP Team App)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://tricountytigers.ca/</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>East Hants sits between Truro and Halifax — check for overlap with the Halifax-region census</t>
         </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1793,58 +1793,58 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>East Preston</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>prestonreccentre@gmail.com</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Charnell Colley — club contact per Basketball Nova Scotia registry (Preston Recreation Centre); role title not published</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Youth teams from U10 up; hosts the annual Easter Classic community tournament in East Preston</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Community-rec-centre-based club in a historic African Nova Scotian community; Easter Classic info hosted at liveinfinitus.com/easterclassic</t>
         </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1858,63 +1858,63 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Fundy (East Hants)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Enfield / Municipality of East Hants</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>registrar.tcba@gmail.com</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>https://tricountytigers.ca/</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Nonprofit (formerly Tri-County Basketball Association); competitive U10-U18 boys &amp; girls teams; Jr NBA ages 5-10; sessions, camps and events; formal constitution/bylaws</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + registrations)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://tricountytigers.ca/</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1928,73 +1928,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Fall River</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>PO Box 2072, Fall River, NS B2T 1K6</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>president@fallriverrebels.com</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://fallriverrebels.com/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Roberta Sullivan — President (BNS registry contact on president@ address)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>House league U8 (co-ed) through U18 boys &amp; girls</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>RAMP InterActive (fallriverrebels.rampregistrations.com)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://fallriverrebels.com/</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Registrar email registrar@fallriverrebels.com also published | Also listed as: Fall River Rebels Basketball Association</t>
         </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -2008,72 +2008,72 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Glace Bay</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>PUSH Arena, 25 May Street, Glace Bay, NS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>(902) 266-2191</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>info@pushcb.com</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>https://pushcb.com</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Tyrone Levingston — founder &amp; head trainer (PUSH = 'Preparation Until Success Happens'; former GM/owner of pro Cape Breton Highlanders, son of Halifax Rainmen owner Andre Levingston)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Ages 6-18: seasonal training blocks (winter/spring/summer/fall, ages 6-16, $500), travel teams U12/U14/U16/U18 ($250), invitation-only elite teams 12-18, in-house game programming, boys skills camp gr 3-8, Small Ball camp, Canada Day Classic tournament, March Madness and Levingston 3-on-3 tournaments, gym rentals</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>PUSH Cape Breton (in-house game programming + Canada Day Classic); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>GoDaddy website + Google Forms registration; Exposure Events organization page for tournaments (basketball.exposureevents.com/organizations/33899)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://pushcb.com/</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>PUSH = 'Preparing Until Success Happens'. Partners with KidSport/Jumpstart for fee assistance despite academy model.</t>
         </is>
@@ -2090,62 +2090,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Glace Bay / New Waterford</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>224 York St, Glace Bay, NS</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>902-849-7559</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>info@undercurrentyouthsociety.com</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>https://undercurrentyouthsociety.com/</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Trevor DenHartogh — Executive Director</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Youth-centre charity serving Glace Bay, New Waterford and surrounding CBRM; recreational basketball among activities (also floor hockey, crossfit)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>multi-sport org</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://undercurrentyouthsociety.com/</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Not a BNS member club; rec programming only — low GTM priority but real basketball provider | Type: nonprofit youth-centre society (basketball is one program within free youth programming; centres in Glace Bay + New Waterford, new Sydney/Glace Bay facility in progress). Address/phone/email/staff from official site (undercurrentyouthsociety.com; undercurrentyc.com redirects there). ED confirmed by CBC (cbc.ca/news/canada/nova-scotia/glace-bay-youth-centre-sod-turning-1.7186943; also newdawn.ca/2025/10/17/transformation-change-taking-place-in-glace-bay/); DenHartogh is also Senior Director of Community Prevention, The Hope Network. Other staff: Megan Syms (Dir. Programming Glace Bay), Chris Kaiser (Dir. Programming New Waterford), Robbie Metcalfe (Programming Supervisor), Sefin Stefura (Project Mgr). Registration handled on own website ('Program Registration' page), not RAMP/TeamLinkt. Also listed on ns.211.ca.</t>
         </is>
@@ -2162,67 +2162,67 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>(782) 234-7481</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>902hoopsns@gmail.com</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>https://902hoops.ca/</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Robbie McGee — CEO / League Director</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Primarily adult summer showcase league (16 teams, YouTube-streamed); also markets a '902 Hoops Elite Youth League' product plus Unity Cup and Draft Season events</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>902 Hoops Elite Youth League (own product)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>private league operator</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>WordPress + WooCommerce (league products sold as e-commerce items)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://902hoops.ca/</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Included for completeness as a youth-league operator; core business is adult league — youth league scale unverified. NEW league not on the pre-mapped list | Largest adult league in Atlantic Canada now expanding to youth: launching U10/U12/U14/U16 divisions ('902 Hoops Elite Youth League', Facebook page https://www.facebook.com/p/902-Hoops-Elite-Youth-League-61574654511468/). Competitive-intel: registration via own WooCommerce shop (902hoops.ca/shop) + Google Forms waiver; uses SportsVisio AI stats/highlights app — no RAMP/TeamLinkt/TeamSnap. Halifax Chamber of Commerce member. Phone per Yelp listing (https://www.yelp.ca/biz/902-hoops-league-halifax). Sources: https://www.sportsvisio.com/stories/from-grassroots-to-greatness-the-tech-driven-rise-of-902-hoops ; https://ca.linkedin.com/in/robbie-mcgee-327866133 ; https://business.halifaxchamber.com/members/member/902-hoops-league-181680 ; https://902hoops.ca/ .</t>
         </is>
@@ -2239,78 +2239,78 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>21</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Community YMCA, 2269 Gottingen St, Halifax, NS B3K 3B7</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>902-423-9622 ext 4</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>trevor.walter@halifax.ymca.ca</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://ymcahfx.ca/panthers/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Brianna Cromwell — Director of the Community Y (program sits under her); BNS registry contacts Brianna Cromwell / Trevor Walter</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Jr. NBA skills program ages 5-7; house/rep teams U10-U18 (beginner to rep, ages 5-18); youth pickup; $375/division for 2026-27 incl. weekly practice + weekly MBA game</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>multi-sport org (YMCA program)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>ACTIVE Network / ActiveCommunities (anc.ca.apm.activecommunities.com/ymcahalifaxdart)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://ymcahfx.ca/panthers/</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Registration also done in person at Community YMCA lobby</t>
         </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2324,57 +2324,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>info@fiftyforfree.com</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>https://fiftyforfree.com/programs/halifax/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Vanessa Smithers — Program Director; Colter Simmonds — Associate Director; Jameel Williams — Lead Coach</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Free 4-week summer camp (Mon-Fri) for ages 13-19 combining high-level basketball training with financial-literacy and professional-development curriculum</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>community nonprofit (free program, not a league club)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>123FormBuilder for registration; WordPress site</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://fiftyforfree.com/programs/halifax/</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Nonprofit free-access youth basketball initiative (national org with Halifax program). Founder/CEO Jermaine Anderson is a retired pro player (MBA, Toronto Metropolitan U). Halifax program staff: Vanessa Smithers (Program Director), Colter Simmonds (Associate Director), Jameel Williams (Lead Coach). Board incl. Courtney Charles (VP Basketball &amp; Franchise Ops, Raptors 905), Kiran Choudhry, Maliha Altaf, Cherilyn Scobie. No street address or phone published. Sources: https://fiftyforfree.com/programs/halifax/ ; https://fiftyforfree.com/about/board/ ; https://fiftyforfree.com/contact-us/ .</t>
         </is>
@@ -2391,68 +2391,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>hhbasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://www.hhbball.com/</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Pete Sonnichsen and Danny De Palma — club contacts per BNS registry (De Palma handles registration/financial assistance); role titles not published</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Mini Canes intro program; U10-U18 competitive teams boys &amp; girls (up to 7 teams per age group); 'Get The Rust Off Runs', spring skills, U12/U14 3v3; $500 regular-season fee. First HRM club to be Canada Basketball 'Club Verified'</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registration, team app, official assigning)</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>One of the largest Halifax-peninsula clubs | Also listed as: Halifax Hurricanes Minor Basketball</t>
         </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -2466,67 +2466,67 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1496 Bedford Hwy, Bedford, NS B4A 1E4</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>902-457-6633</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>admin@mingathleticsmail.com</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>https://halifaxprep.com/</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Naofall 'Ming' Folahan — President, Co-Founder &amp; Head Coach (former Wagner College D1 player, NBL Canada); co-founded with wife Stephanie Folahan; operated via M7NG Company / Halifax Basketball Inc.</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Prep (high-school-age) elite travel teams with national livestreamed schedule and scouting exposure; youth skills camps; ~$5,000/yr tuition incl. full facility access; in-house trainers, massage therapist, barber; 100% graduation rate claimed. Founded 2017; facility = converted former Olympia Theatre building (basketball-only); early roots reported in Spryfield</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>National Preparatory Association (NPA) — Nova Scotia's only member; National Senior Circuit (NSC Platinum, 2020-21 season); National Preparatory Association (NPA); National Senior Circuit (NSC Platinum, 2020-21)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://www.cbc.ca/news/canada/nova-scotia/halifax-basketball-club-vandalism-struggles-for-acceptance-1.5973342</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>halifaxprep.com and mingathletics.com both failed DNS at research time — verify current operating status before outreach; CBC (Mar 2021) covered the club's facility vandalism and $5K/yr model | Type: private academy/prep program (Halifax Prep Basketball Inc., founded 2017, based in Spryfield; brands: Ming Athletics, Halifax Basketball). Principal + email verified from archived mingathletics.com About page (web.archive.org/web/20191206032913/https://mingathletics.com/about-us) — email is 2019-vintage, treat as stale. STATUS WARNING: all three domains dead/blocked as of 2026-07-14 (halifaxprep.com + mingathletics.com no DNS; halifaxbasketball.com hard 403); last independent coverage ~2021-22 (CBC vandalism story cbc.ca/news/canada/nova-scotia/halifax-basketball-club-vandalism-struggles-for-acceptance-1.5973342; wagner.edu/wagnermagazine/mings-next-chapter/). Possibly defunct or rebranded — verify before outreach. Not on current Basketball NS member-club list (basketballnovascotia.ca/content/member-clubs). Advisory board (2019 archive of halifaxprep.com/hp-board): Dr. Robert Abraham, Kurt Benson, Shaun Carvery, Kevin Springer, Thane Smith. | Also listed as: Halifax Prep (Ming Athletics)</t>
         </is>
@@ -2543,52 +2543,52 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>HWCBBC@gmail.com</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>https://www.facebook.com/nswheelchairbasketball/</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Cher Smith — club contact (BNS registry)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Wheelchair basketball (parasport); age range not published — may be mixed youth/adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>community nonprofit (parasport)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>BNS member club; youth-specific programming unconfirmed — flag for follow-up rather than exclude</t>
         </is>
@@ -2605,57 +2605,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>5604 Morris Street, Halifax, NS B3J 1C2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>dgt@c-ntr-l.org</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://highlevelbasketball.org/</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Private training academy: small-group sessions (max 6, grade 5+), 1-on-1/semi-private training, 4-week structured programs, summer camp 2026. No league teams found</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Shopify (e-commerce/session booking)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://highlevelbasketball.org/</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Training-only operator; not a BNS member club | Type: private academy/training business (1-on-1, private group, 4-week small-group programs). Address + email from its own privacy policy (highlevelbasketball.org/policies/privacy-policy). CAVEAT: email domain c-ntr-l.org is a parked 'coming soon' site — may be boilerplate/owner side-project; primary contact is the site form (highlevelbasketball.org/pages/contact). Platform intel: runs on SHOPIFY for registration/booking (not RAMP/TeamLinkt). Instagram: @high.level.basketball. No leadership names published anywhere found; not on current Basketball NS member-club list.</t>
         </is>
@@ -2672,57 +2672,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>902-471-4023</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>https://www.thunderselects.ca/</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Brandon Rafuse — Founder &amp; Director</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Girls-only (U21 and younger): ELITE summer team program, ACADEMY/NEXT/Hoop School skills training, East Coast Invitational event, Halifax Thunder Fall League; alumni placed at 23 Canadian universities</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Halifax Thunder Fall League (own league); Maritime Women's Basketball Association (MWBA — senior Halifax Thunder team; adult league, noted for context)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>uKit website (built by SKYSAIL); email obfuscated on site</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://www.thunderselects.ca/</t>
         </is>
@@ -2739,72 +2739,72 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Halifax</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Ummah Community Centre (UMCC), 2510 Matthias Street, Halifax, NS B3L 0A9</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>+1 902-407-1411</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>info@ummahsociety.ca</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>https://ummahsociety.ca/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Imam Abdallah Yousri — CEO</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Young Sisters Basketball and other youth recreation programming; UMCC gym is host venue for the Nova Scotia Valour League (All Canada Basketball, ages ~U11-U16, run by Imad Qahwash, iqahwash@allcanadabasketball.com)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Nova Scotia Valour League (All Canada Basketball) — as host venue</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>multi-sport community org (Muslim charity)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>MOHID (mosque management/registration platform)</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://ummahsociety.ca/</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Not a BNS member club; captured as community youth-basketball provider and Valour League venue | Community association — largest Muslim charity in Atlantic Canada (founded 1984); Ummah Community Center described as 'a hub for sports clubs, sports tournaments and community games'; basketball/youth sports run through the licensed community centre rather than as a standalone club. No dedicated basketball-program director identified. Sources: https://ummahsociety.ca/ ; https://ummahsociety.ca/about/ ; https://ca.linkedin.com/in/abdallah-yousri-379021131 .</t>
         </is>
@@ -2821,58 +2821,58 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Halifax (HRM — exact community unverified)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>sandiehebb@gmail.com</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Sandie Hebb — club contact (BNS registry)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Youth teams in MBA divisions (U12-U16 per MBA team pages)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>No club website found; home community within HRM not published — needs follow-up</t>
         </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2886,68 +2886,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="n">
+        <v>21</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>https://www.expressbasketball.ca/</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Abigail Stewart — club contact (BNS registry)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Competitive/rep + developmental teams U10-U16 boys &amp; girls; serves Spryfield and communities on the Sambro loop; deliberately low registration cost; established 1999</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + registration + team app)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://www.expressbasketball.ca/</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Despite 'Academy' name in BNS registry, self-describes as low-cost community club</t>
         </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -2961,68 +2961,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="n">
+        <v>21</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Halifax (Spryfield)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>info.expressbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>https://expressbasketball.ca/</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Abigail Stewart — club contact per Basketball Nova Scotia registry; role title not published</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Competitive and developmental teams U10-U16 boys &amp; girls; established 1999; serves Spryfield and surrounding loop to Sambro; low registration costs</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registration, official assigning, team app)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Listed as 'Express Basketball Academy' in BNS registry but self-describes as a community club, est. 1999 — not a private academy</t>
         </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="36">
@@ -3036,68 +3036,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="n">
+        <v>33</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Halifax (west end)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>president@westendsteelers.com</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>http://westendsteelers.com/</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>John Hope (john.hope@dal.ca) — club contact per BNS registry; president reachable at president@westendsteelers.com; president's name not published</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Youth basketball across MBA age groups; 500+ registered players last season — among the largest HRM clubs</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>GOALLINE (site 'Powered by GOALLINE'); also a SportsEngine org directory listing. Site returned 500 at fetch time</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>GOALLINE stack = competitive intel (one of two GOALLINE clubs in HRM alongside Dartmouth Celtics; BNS Provincials also run on GOALLINE)</t>
         </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -3111,68 +3111,68 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Halifax/Dartmouth (Greater HRM)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>cgabriel901@gmail.com</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>https://www.tricityvipers.ca/</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Curtis Gabriel — club contact per BNS registry and coach of Vipers MBA teams; club founded ~2016 as AAU-style competitive program ('premiere AAU organization for Youth Basketball in the Greater Halifax/Dartmouth Area')</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Competitive club teams U10-U18 boys &amp; girls; fall/winter club registration; GOLD tier program (e.g. U14 girls); skill development focus, athletic + academic prep</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>community nonprofit (competitive/AAU-style club)</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>RAMP InterActive (website, registration, official assigning, team app); also has a SportsEngine org directory listing</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Nonprofit status not formally confirmed; operates as a competitive club rather than neighbourhood house-league association</t>
         </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -3186,47 +3186,47 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Hantsport</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>902-684-9672</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Renda Vandertoorn — contact (Valley Family Fun directory)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Youth leagues in Hantsport</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://valleyfamilyfun.ca/basketball/</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Directory-only evidence; not on 2025-26 BNS member list — may be inactive or absorbed by Shooting Star (Windsor is adjacent). Verify before outreach</t>
         </is>
@@ -3243,62 +3243,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Inverness</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>philblackwood@gmail.com</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/359820744477615/</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Phil Blackwood — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Minor basketball for Inverness (western Cape Breton)</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Facebook group only</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>BNS registry member; Facebook-group-only presence. | Community association; Basketball Nova Scotia member club (Cape Breton region, Fall/Winter club) — registry lists contact Phil Blackwood, philblackwood@gmail.com (role not stated, so not recorded as principal). Online presence is a Facebook group only; no website, address, or phone found. BNS registry is RAMP-hosted. Source: https://basketballnovascotia.ca/content/member-clubs .</t>
         </is>
@@ -3315,57 +3315,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Kentville</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>shotclock2016@gmail.com</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>https://www.facebook.com/BasetballAssociationofKentville/</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>House leagues for children aged 5+ in Kentville (the 'Basketball Association of Kentville' house league already mapped as a league)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Basketball Association of Kentville; Basketball Association of Kentville (own house league)</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Facebook page; no registration storefront found</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://valleyfamilyfun.ca/basketball/</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Not on 2025-26 BNS member list | Type: community association/recreational league (kids 5+). Email from Valley Family Fun community sports directory (valleyfamilyfun.ca/basketball/); Facebook page (handle misspelled 'BasetballAssociationofKentville') is the only web presence — no website, address, phone, or named officers found. Former Valley Connect / CIOC directory record TOK0041 (valleyconnect.cioc.ca/record/TOK0041) is decommissioned and not archived. Not on current BNS member-club list. Enrichment would need a Facebook message or Town of Kentville recreation department referral (kentville.ca/parks-and-recreation).</t>
         </is>
@@ -3382,57 +3382,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Kentville</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Kentville, NS B4N 1T6</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://www.sportsengine.com/org/kentville-wildcats-basketball</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Rep/travel youth teams under 'Kentville Minor Basketball Association'; historical entries in BNS provincials (GOALLINE era); legacy 'Jr Axewomen &amp; Kentville Wildcats' eteamz site</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>SportsEngine org listing (legacy Sport Ngin); eteamz legacy site</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://www.sportsengine.com/org/kentville-wildcats-basketball</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Possibly the rep arm of/predecessor to the Basketball Association of Kentville; the current senior 'Kentville Wildcats' team in NSSBL is adult — excluded. A separate baseball 'Kentville Wildcats' exists in Baseball NS's Bluenose League — do not conflate | LIKELY DEFUNCT / STALE LISTING. The SportsEngine org page is an unclaimed directory shell ('Claim This Organization') giving only 'Kentville, NS B4N 1T6' and a dead eteamz site (www.eteamz.com/kentvillebasketball/ — eteamz platform shut down). No current 'Kentville Wildcats' basketball activity found; all active Kentville Wildcats teams located are BASEBALL (BNS Bluenose League on RAMP, e.g. bluenoseleague.ca/team/6517/1436/13070/137977). Active youth basketball in Kentville today = Basketball Association of Kentville (separate entry). Recommend dropping or merging this record. Source: sportsengine.com/org/kentville-wildcats-basketball.</t>
         </is>
@@ -3449,63 +3449,63 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Annapolis Valley</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Kentville (serves Hantsport to New Minas corridor)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>U8, U10 (3x3), U12, U14, U16 + STRIVE competitive stream; ~$5/athlete/hr pricing; financial assistance program; formed from merger of Hantsport Minor Basketball, Port Williams Hawks, and Acadia Minor Basketball; partnership with Acadia University</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>RAMP Registrations; Squarespace-style website</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>The consolidated Valley club — absorbed three predecessor orgs. Safeguarding policies published (Rule of Two, anti-discrimination).</t>
         </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="43">
@@ -3519,62 +3519,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Kingston / Greenwood</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>jodie-richardson@hotmail.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>https://www.facebook.com/people/Kingston-Greenwood-Minor-Basketball-Club/100063571598747/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Jodie Richardson — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Minor basketball for Kingston/Greenwood (14 Wing area, Annapolis Valley); Axe Basketball lists games between Wolfville and Greenwood, implying inter-club Valley play</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Facebook page only</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Valley Family Fun lists a 'Greenwood Minor Ball' contact (ggullison@ns.sympatico.ca, 902-765-6689) on its basketball page — possibly this club, unconfirmed</t>
         </is>
@@ -3591,62 +3591,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>South Shore</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Liverpool (Region of Queens)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>gerryfaber@hotmail.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>https://www.facebook.com/qcbasketball/</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Gerry Faber — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Basketball programming for Queens County residents; 'Queens County Bears' is the BNS-registered club identity</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Facebook only</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Region of Queens rec dept (902-354-3453) is the practical referral point; club absent from municipal org directory. | Type: community club (BNS member as 'Queens County Bears', South Shore region, Fall/Winter). BNS-listed club contact: Gerry Faber (role not stated) — source: https://basketballnovascotia.ca/content/member-clubs. Facebook page: https://www.facebook.com/qcbasketball/. No registration platform identified.</t>
         </is>
@@ -3663,57 +3663,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Lower Sackville</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>president@sackvillestorm.com</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>https://www.sackvillestorm.com/</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>David Barrett — President (BNS registry contact using president@ address)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Jr. NBA; U10/U12/U14 girls &amp; boys; U16 boys; U18 boys; dryland training</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>RAMP InterActive (SackvilleMinorBasketball.rampregistrations.com + RAMP Team app)</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
@@ -3730,62 +3730,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Cape Breton</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Margaree</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>margareemountainlionsbball@gmail.com</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61557417235365</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>James Bennett Shaw — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Small rural club (Margaree Valley, Inverness County)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Facebook only</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>BNS registry member; no further web presence found. | Community association; Basketball Nova Scotia member club (Cape Breton region, Fall/Winter club) — registry lists contact James Bennett Shaw with club email margareemountainlionsbball@gmail.com (role not stated, so not recorded as principal). Online presence is a Facebook page only (created ~2024 per page ID format); no website, address, or phone found. BNS registry is RAMP-hosted. Source: https://basketballnovascotia.ca/content/member-clubs .</t>
         </is>
@@ -3802,52 +3802,52 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Fundy (Colchester/Cumberland North Shore)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>NS North Shore (Tatamagouche–Pugwash corridor; exact town not published)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>30 Blair Avenue, Tatamagouche, NS B0K 1V0</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>902-657-3121</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>northshorereccentre@gmail.com</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Richard Halverson, Manager</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>BNS registry-only (Fundy region). North Shore Recreation Centre in Tatamagouche is the area's sports hub — likely venue; unconfirmed. | enriched 2026-07-18</t>
         </is>
@@ -3864,57 +3864,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>hislopjw@gmail.com</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>https://www.pictoucountylightning.com/</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>John Hislop — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Rep club teams 2025-26: U12 boys x2 (Barker/Fraser, Budge/Hayward), U12 girls (MacKinnon), U14 boys x3 (Russell, Snell, El Haddad), U14 girls (MacGregor); also fields U18 (played Kings County U18, 2024)</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + RAMP Registration + RAMP Team App)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://www.pictoucountylightning.com/</t>
         </is>
@@ -3931,57 +3931,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>New Glasgow / Pictou County</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>sports3taxi@hotmail.com</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>https://www.basketballnovascotia.ca/team/pictou-county-raptors-2/</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Maureen MacDonald — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Rep teams including U14 girls (BNS U14 Girls Division 1, 2026)</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships; BNS Provincial Club Championships (U12 / U14 / U16-U18 Provincials)</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Second Pictou County club alongside the Lightning</t>
         </is>
@@ -3998,57 +3998,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>North Preston</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>northprestonbulls@gmail.com</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>https://www.instagram.com/north_preston_bulls/</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Corvell Beals — club contact per Basketball Nova Scotia registry; role title not published</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Youth teams from U10 up; competes in community events like the East Preston Easter Classic</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Instagram: north_preston_bulls. MBA membership rated reported-strength (division-page evidence, no club page)</t>
         </is>
@@ -4065,57 +4065,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Cape Breton</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>North Sydney / Northside area, Cape Breton</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>aronashton4@gmail.com</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>http://www.jrmarauders.com/</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Aron Ashton — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Youth basketball for Cape Breton's Northside (Jr Marauders branding aligns with Memorial High Marauders feeder area)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Listed on BNS member-club registry (Cape Breton region) with no website; no independent web presence found — needs direct outreach. | Community association; Basketball Nova Scotia member club (Cape Breton region, Fall/Winter club) — registry lists contact Aron Ashton, aronashton4@gmail.com (role not stated; not confirmed as president, so left out of principal). Club email admin@jrmarauders.com also surfaced via the BNS listing. jrmarauders.com is a 'Launching Soon' placeholder with only a signup form. Long-running program — builders Dave Young, Brian Purchase, Bobby Gardner honoured for Jr. Marauders contributions (Simon tourney HOF 2023). BNS registry is RAMP-hosted (competitive intel: RAMP InterActive). Sources: https://basketballnovascotia.ca/content/member-clubs ; http://www.jrmarauders.com/ ; https://www.thesimontourney.com/post/hof-2023 .</t>
         </is>
@@ -4132,52 +4132,52 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Oxford</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>oxfordminorhoops@gmail.com</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Michelle Embree — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Minor basketball for the town of Oxford, Cumberland County</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>BNS registry-only entry; no web presence found.</t>
         </is>
@@ -4194,57 +4194,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Prospect Road area (Halifax)</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>prospectbulls1@gmail.com</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>https://www.prospectbulls.ca/</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Morgan McWade — club contact (BNS registry)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Junior/Mini Bulls intro; house league and competitive teams U10, U12, U14, U16/18</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + registration + team app)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://www.prospectbulls.ca/</t>
         </is>
@@ -4261,62 +4261,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>South Shore (Shelburne County)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Shelburne / Shelburne County</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>beth.shelburnebasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/ShelburneCountyBasketball/</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Beth VanBuskirk — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Youth basketball across Shelburne County; fields 'Wildcats' teams at BNS Provincials; associated 'Shelburne County Kings Basketball Club' offers spring/summer U14-U18 teams</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships (U12 / U14 / U16-U18 Provincials); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Facebook group only</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Do NOT confuse with 'Shelburne Shocks' (that is Shelburne, Ontario). Kings club relationship (same org's rep arm vs separate club) unverified. | Type: community club (BNS member, South Shore region, Fall/Winter). BNS-listed club contact: Beth VanBuskirk (role not stated; email pattern suggests association-dedicated address) — source: https://basketballnovascotia.ca/content/member-clubs. Only web presence is Facebook group: https://www.facebook.com/groups/ShelburneCountyBasketball/. No registration platform identified.</t>
         </is>
@@ -4333,52 +4333,52 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Fundy (East Hants)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Shubenacadie / East Hants</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>902-750-0619</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>http://www.ehhavoc.org/</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Volunteer-run society; Havoc Recreational League (equal-playing-time house league; registration delayed to 2025 for volunteer shortage); has fielded competitive teams (e.g. Havoc U16)</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>TeamLinkt (explicitly switched FROM TeamSnap, citing preference for a Canadian company)</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>http://www.ehhavoc.org/havoc/EHBSMissionVisionValues</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>KEY COMPETITIVE INTEL: publicly announced TeamSnap→TeamLinkt migration on 'support Canadian company' grounds — exactly the switching narrative SportsHub competes in.</t>
         </is>
@@ -4395,62 +4395,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Sydney</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>cbdreambasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/cbdreambasketball/home</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>James Williams — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Newly established (c.2025) girls-only club; original U14 team, growing to more age groups; Canada Basketball Verified; runs its own tournament</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Google Sites website; registration platform not identified</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>FB posts reference a busy month of practices, games and travel — plays somewhere (likely BNS events) but league not published.</t>
         </is>
@@ -4467,73 +4467,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Cape Breton</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Sydney / Glace Bay (CBRM)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Former Bridgeport school, Glace Bay, NS (training hub); summer programs held at Cape Breton University, Sydney</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Summer2026@basketballcapebreton.com</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>https://linktr.ee/basketballcb</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Chris MacPhee — Vice President (per ZoomInfo; president not published)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Nonprofit founded 2012, ~500 youth across CBRM; middle/high-school training sessions, free Tip-Off drop-ins, Youth Camp (b.2015-2019, $150), Intermediate Camp (b.2012-2015, $150), summer league</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Basketball Cape Breton Summer League; BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Google Forms for all registrations (no RAMP/TeamLinkt); Linktree front door</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Largest youth basketball org on Cape Breton Island. CBC (2015) covered its move into former Bridgeport school in Glace Bay. Google-Forms-only registration = greenfield software prospect.</t>
         </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -4547,73 +4547,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="n">
+        <v>38</v>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Halifax Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Tantallon / St. Margaret's Bay</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>St. Margaret's Centre (12 Westwood Blvd area, Upper Tantallon) — street address not published on site</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>information@slambasketball.ca</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>https://slambasketball.ca/</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Jonathan Stevens and Andrea Johnston (andrea@slambasketball.ca) — club contacts per BNS registry; role titles not published</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Jr. NBA U6/U8 12-week program; house-league teams U10-U18 boys &amp; girls (practice weekly + weekend Metro league game); spring 5-week fundamental skills sessions. Est. 1999 with 96 players, now ~500 annually; serves St. Margaret's Bay, Tantallon, Timberlea, Hammonds Plains</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA)</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + registration)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Covers the western HRM commuter belt (Timberlea/Hammonds Plains have no separate club)</t>
         </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -4627,62 +4627,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Tatamagouche / North Shore</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>30 Blair Avenue, Tatamagouche, NS B0K 1V0</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>902-657-3121</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>northshoresonicsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Dan MacDonald — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Youth basketball for the North Shore corridor (Tatamagouche-Pugwash-Wentworth-River John area)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>enriched 2026-07-18</t>
         </is>
@@ -4699,62 +4699,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Truro</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>cba.trurobball@gmail.com</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/69056384036/</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Donnie MacGregor — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Youth basketball for Colchester County; Jr NBA youth division (ages 7-9) historically run at Truro Elementary on Sundays</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Former GOALLINE/Stack Sports site (colchesterbasketballassociation.goalline.ca — now dead, redirects to stacksports.com); currently Facebook group</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Relationship to Truro Titans (same town) unclear — both currently exist; colchesterbasketball.org LeagueApps portal found in search is a different (US) organization, do not attribute</t>
         </is>
@@ -4771,72 +4771,72 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Truro</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>PO Box 25002, 179 Esplanade St., Truro, NS B2N 7B8</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>902-843-9306</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>trurotitansbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>https://trurotitansbasketball.net</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Kevin Jones — Coordinator/President</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>U10 &amp; U12 programs with 3v3 intrasquad and 4v4/5v5 competitive exhibition games; older rep teams entered in MBA (U12 'Robson' and a U16 boys 'Preiss' team on 2025-26 MBA site)</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>RAMP InterActive website (trurotitansbasketball.net — DNS intermittently unresolvable); formerly GOALLINE (trurotitansbasketball.ca, dead)</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>https://mbans.ca/team/4532/922/10347/117160</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>A search-snippet claim naming a president could not be verified against a live page — omitted. Notably NOT on the 2025-26 BNS member-club list (Colchester Basketball Association is the listed Truro-area member) | Type: community rep/club association (volunteer not-for-profit, U7–U18 competitive). Phone + email confirmed on current-generation RAMP site footer (archived Jul 2025: web.archive.org/web/20250717114401/https://trurotitansbasketball.net/). Address + full executive from association's 2019 record-check letter on prior GOALLINE site (web.archive.org/web/20220507131242/http://trurotitansbasketball.ca/page.php?page_id=116826): Pres. Kevin Jones, VP Jan Murray, Financial Officer Valerie Patterson, Members-at-Large David Barrington &amp; Robert Ritacco — executive names are 2019-vintage, may be stale. Platform intel: migrated GOALLINE -&gt; RAMP InterActive. WARNING: trurotitansbasketball.net has no DNS as of 2026-07-14 (site may be lapsed); teams still appear in Metro Basketball Association (RAMP, mbans.ca). Not on current BNS member-club list (nearby Colchester Basketball Association is).</t>
         </is>
@@ -4853,62 +4853,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>West Hants, NS (OUTSIDE Halifax Regional Municipality — encountered during sweep)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Windsor</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>43 Campbell Avenue, Windsor, NS</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>+1 902-692-1123</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>info@superhoopsbasketball.ca</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>https://superhoopsbasketball.ca/</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Coaching team: Nick Jordan (Head Coach, also BNS U15 Girls provincial head coach), Emma Duinker and Abbey Duinker (coaches, ex-Acadia/pro Europe); owner/founder not explicitly stated</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Training camps and clinics for young players, beginner to advanced; no evidence of fielding league teams</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://superhoopsbasketball.ca/</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Outside HRM (Windsor, Hants County — same town as Shooting Star Basketball's house leagues); captured because encountered during the HRM sweep — assign to Valley/Fundy region pass for dedupe</t>
         </is>
@@ -4925,73 +4925,73 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Windsor (West Hants)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>West Hants Regional Municipality, NS</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>shootingstar@shootingstarbasketball.ca</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>https://shootingstarbasketball.ca/</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Tim Bachiu — club contact (BNS member registry) and coach</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Little Dribblers (entry level), U10/U12/U14/U16 boys &amp; girls; house leagues in Windsor (already mapped as a league); Canada Basketball Verified with mandatory background checks/Safe Sport for coaches</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League); Shooting Star Basketball Association house leagues (Windsor); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>RAMP InterActive (website + RAMP Registration). Secondary registrar email: registrarSSBA@gmail.com</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://shootingstarbasketball.ca/</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Also listed as: Shooting Star Basketball Association</t>
         </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -5005,57 +5005,57 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Wolfville</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>1-15 Locust Ave, Wolfville, NS B4P 1G2</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>1-902-670-7936</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>https://www.acadiaminorbasketball.ca/</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Jeff Hanshaw — club contact (role not stated)</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Community club for Wolfville and area, 'programs for kids grade 1+' — opportunities to learn, play and develop regardless of age, gender or ability</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>https://valleyfamilyfun.ca/basketball/</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Website no longer resolves; not on 2025-26 BNS member list — possibly dormant or superseded by Axe Basketball Club (same town). Verify before outreach | Type: community minor-basketball club (grade 1+, mini to midget/U18). Address, phone, contact name from archived Joomla Contact Us page (web.archive.org/web/20180406183238/http://www.acadiaminorbasketball.ca:80/index.php/contact-us) — 2018-vintage; email was form-only. WARNING: own domain dead (hosting-suspended page in 2025 archives; no DNS 2026-07-14), so contact data is stale. Club still fields teams in Metro Basketball Association on RAMP (e.g. 'Acadia Minor - Tucker': mbans.ca/team/7000/923/10350/161342/player/2022811) — platform intel: league play via RAMP. Directory corroboration: zaubee.com/biz/acadia-minor-basketball-65cq14ra (15 Locust Ave #1). Not on current BNS member-club list (Kings Minor Basketball covers adjacent area).</t>
         </is>
@@ -5072,63 +5072,63 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" t="n">
+        <v>9</v>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>Rest of Nova Scotia</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Wolfville</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>axebasketballclub@gmail.com</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>https://www.axebasketball.ca/</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Len Harvey — club contact (BNS member registry); volunteer board of directors</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>U8, U10, U12, U14, U16 programs; 3x3 development; STRIVE (U12); U10 Sunday 3x3 sessions with Acadia Axemen/Axewomen varsity players; games between Wolfville and Greenwood</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>Metro Basketball Association (MBA / Metro Basketball League); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Squarespace website + RAMP Registrations</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>https://www.axebasketball.ca/</t>
         </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -5142,62 +5142,62 @@
           <t>Nova Scotia</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>South Shore / Southwest (Yarmouth County)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Yarmouth</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>yarmouthminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>https://www.facebook.com/yarmouthminorbasketball/</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Jonathan Ettinger — club contact (BNS member registry)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Basketball for Yarmouth-area youth ages 5-17</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>BNS Provincial Club Championships (U12 / U14 / U16-U18 Provincials); BNS Provincial Club Championships</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Facebook only</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>https://basketballnovascotia.ca/content/member-clubs</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>Neil Deveau is the Yarmouth-area rep for NS Basketball Officials (nsbo.ca) — potential local referral contact, not a club principal. | Type: community minor basketball club (BNS member, South Shore region, Fall/Winter). BNS-listed club contact: Jonathan Ettinger (role not stated) — source: https://basketballnovascotia.ca/content/member-clubs. Facebook page: https://www.facebook.com/yarmouthminorbasketball/. Association-dedicated gmail address suggests generic inbox usable for outreach. No registration platform identified.</t>
         </is>
